--- a/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
+++ b/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
+++ b/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
+++ b/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -627,7 +627,6 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="34131-3"/&gt;
-    &lt;display value="Outpatient Progress note"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
+++ b/output/StructureDefinition-t-cabs-diagnosticreport-visitenbefund.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-diagnosticreport-visitenbefund</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-diagnosticreport-visitenbefund</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,7 +656,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -688,7 +688,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-encounter-kontakt)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-encounter-kontakt)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparameter|http://t-cabs.org/StructureDefinition/t-cabs-observation-vitalparameter)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparameter|https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-vitalparameter)
 </t>
   </si>
   <si>
@@ -1398,7 +1398,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="128.40234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="153.04296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
